--- a/search_model_2Type/log/Est1.xlsx
+++ b/search_model_2Type/log/Est1.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120.0045211914216</v>
+        <v>119.989129700929</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03611278220501103</v>
+        <v>0.03614897227100273</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.126550195284722</v>
+        <v>0.1248944248849519</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.36209950287632</v>
+        <v>30.41931916242401</v>
       </c>
     </row>
     <row r="10">

--- a/search_model_2Type/log/Est1.xlsx
+++ b/search_model_2Type/log/Est1.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>119.989129700929</v>
+        <v>108.2166441767175</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03614897227100273</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1248944248849519</v>
+        <v>0.0558233844017595</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.41931916242401</v>
+        <v>12.75921584900898</v>
       </c>
     </row>
     <row r="10">

--- a/search_model_2Type/log/Est1.xlsx
+++ b/search_model_2Type/log/Est1.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>108.2166441767175</v>
+        <v>120.0311822806177</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.15</v>
+        <v>0.03603591601069343</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0558233844017595</v>
+        <v>0.1268601323937932</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.75921584900898</v>
+        <v>30.39064927936741</v>
       </c>
     </row>
     <row r="10">

--- a/search_model_2Type/log/Est1.xlsx
+++ b/search_model_2Type/log/Est1.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120.0311822806177</v>
+        <v>188.136026524236</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03603591601069343</v>
+        <v>0.122253385050994</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1268601323937932</v>
+        <v>0.2519613179064277</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.39064927936741</v>
+        <v>174.0750233259787</v>
       </c>
     </row>
     <row r="10">

--- a/search_model_2Type/log/Est1.xlsx
+++ b/search_model_2Type/log/Est1.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>188.136026524236</v>
+        <v>176.7342607838204</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.122253385050994</v>
+        <v>0.0220929785982211</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2519613179064277</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>174.0750233259787</v>
+        <v>66.00102793931126</v>
       </c>
     </row>
     <row r="10">

--- a/search_model_2Type/log/Est1.xlsx
+++ b/search_model_2Type/log/Est1.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>176.7342607838204</v>
+        <v>41.53637848619653</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0220929785982211</v>
+        <v>0.02362967956904342</v>
       </c>
     </row>
     <row r="5">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66.00102793931126</v>
+        <v>134.2270860045776</v>
       </c>
     </row>
     <row r="10">

--- a/search_model_2Type/log/Est1.xlsx
+++ b/search_model_2Type/log/Est1.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.53637848619653</v>
+        <v>176.7342694373218</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02362967956904342</v>
+        <v>0.02209299473726897</v>
       </c>
     </row>
     <row r="5">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134.2270860045776</v>
+        <v>66.00100762194057</v>
       </c>
     </row>
     <row r="10">

--- a/search_model_2Type/log/Est1.xlsx
+++ b/search_model_2Type/log/Est1.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>176.7342694373218</v>
+        <v>91.20873239059307</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02209299473726897</v>
+        <v>0.02070066029809298</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.25</v>
+        <v>0.2555996784967091</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66.00100762194057</v>
+        <v>165.7760387776958</v>
       </c>
     </row>
     <row r="10">

--- a/search_model_2Type/log/Est1.xlsx
+++ b/search_model_2Type/log/Est1.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91.20873239059307</v>
+        <v>138.9446586850285</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02070066029809298</v>
+        <v>0.02018113546029773</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2555996784967091</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>165.7760387776958</v>
+        <v>49.75066741648185</v>
       </c>
     </row>
     <row r="10">

--- a/search_model_2Type/log/Est1.xlsx
+++ b/search_model_2Type/log/Est1.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138.9446586850285</v>
+        <v>49.75058048002661</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02018113546029773</v>
+        <v>0.02018116284753834</v>
       </c>
     </row>
     <row r="5">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49.75066741648185</v>
+        <v>138.9446670258465</v>
       </c>
     </row>
     <row r="10">

--- a/search_model_2Type/log/Est1.xlsx
+++ b/search_model_2Type/log/Est1.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49.75058048002661</v>
+        <v>126.0441207129484</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02018116284753834</v>
+        <v>0.0130550523442168</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.25</v>
+        <v>0.3247730891221572</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138.9446670258465</v>
+        <v>234.6418057082953</v>
       </c>
     </row>
     <row r="10">
